--- a/04_Kernel_Functions/data/comparativa_benchmark_sinteticos.xlsx
+++ b/04_Kernel_Functions/data/comparativa_benchmark_sinteticos.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0602</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -471,15 +471,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0452</v>
+        <v>0.0311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5 / 100</t>
+          <t>4 / 100</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0805</v>
+        <v>0.1057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
